--- a/payment_forms/023_e_commerce_transaction_compliance_verification_form--payment_forms.xlsx
+++ b/payment_forms/023_e_commerce_transaction_compliance_verification_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1126,8 +1126,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'stripe'}</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Stripe'}</t>
+          <t>Stripe</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'authorize.net'}</t>
+          <t>authorize.net</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Authorize.net'}</t>
+          <t>Authorize.net</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'one-time_transaction'}</t>
+          <t>one-time_transaction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'One-time transaction'}</t>
+          <t>One-time transaction</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'recurring_payment'}</t>
+          <t>recurring_payment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Recurring payment'}</t>
+          <t>Recurring payment</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'subscription'}</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Subscription'}</t>
+          <t>Subscription</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Declined'}</t>
+          <t>Declined</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'error'}</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Error'}</t>
+          <t>Error</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'refunded'}</t>
+          <t>refunded</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Refunded'}</t>
+          <t>Refunded</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Declined'}</t>
+          <t>Declined</t>
         </is>
       </c>
     </row>
